--- a/daily_matches/job_matches_2026-08-01.xlsx
+++ b/daily_matches/job_matches_2026-08-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enterprise / Solution Architect</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, Hugging Face, S3, Glue, Redshift, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>RAG, Glue, Redshift, BigQuery, Synapse, Data Lake, Kinesis, Apache Airflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea47f9494f78051</t>
+          <t>https://www.indeed.com/viewjob?jk=1f0ae34753ca05b6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Apache Spark Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>27.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, BigQuery, CI/CD, GitHub Actions, Terraform, Git, Snowflake, BigQuery</t>
+          <t>Machine Learning Engineer, RAG, S3, Glue, Synapse, Data Lake, MLflow, Docker, Kubernetes, Apache Airflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8024a2005fb0b3ea</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Transflo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>25.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, Snowflake, Kafka, MongoDB, SQL</t>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, Data Lake, Kinesis, Apache Airflow, Terraform, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
+          <t>https://www.indeed.com/viewjob?jk=858aa20205dd4518</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior MLOps &amp; Generative AI Engineer - Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Century Investments</t>
+          <t>Sentara</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Git, Redshift, PostgreSQL, NoSQL, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f0b0aed89dff9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=74f06453e64c4e37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Data Lake, Kinesis, MLflow, Kubernetes, CI/CD, Terraform, Databricks, PySpark, Kafka</t>
+          <t>Data Scientist, RAG, Redshift, Data Lake, CI/CD, Jenkins, Git, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fcc3b31ffee88c1</t>
+          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IS Quality Assurance Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Menards</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R</t>
+          <t>Data Scientist, RAG, Redshift, Data Lake, CI/CD, Jenkins, Git, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b40c6fd6d66400</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, PostgreSQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
+          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Remote)</t>
+          <t>Senior Quantitative Analytics Specialist (Senior GenAI Data Scientist)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, spaCy, NLTK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
+          <t>https://www.indeed.com/viewjob?jk=96de5ccdcd73df96</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>Senior Quantitative Analytics Specialist (Senior GenAI Data Scientist)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Motive</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kinesis, Kafka, PostgreSQL, Cassandra, NoSQL, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, spaCy, NLTK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f3c0b5154214b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f164050cfc69083</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+          <t>RAG, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
+          <t>https://www.indeed.com/viewjob?jk=446f18fd0ddebaff</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Data Platform Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Glue, Athena, Redshift, CI/CD, Terraform, Redshift, Python, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c58a13ba0149da0</t>
+          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S3, Git, Snowflake, Databricks, NoSQL, Tableau, Python, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Workiva</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Cortex, S3, Snowflake, Tableau, Quicksight, Python, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094ac7b7f209413b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Business Analytics Advisor, Payment Integrity - Cigna Healthcare - Remote</t>
+          <t>Senior Software Engineer, AI &amp; Salesforce</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, S3, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db7ff4b63c4808a2</t>
+          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Copilot, Git, Snowflake, Databricks, PySpark, Polars, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6582ecdf9efb1dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Copilot, Git, Snowflake, Databricks, Python, SQL, R, Optimization, Bayesian</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c77f7ef79e88b2a</t>
+          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer- Life Sciences</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Python, R</t>
+          <t>RAG, S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7647b4a3d3ef08f</t>
+          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer - Life Science</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1624a603cf13b66a</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Idira Secrets SME - Domain Consultant</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Prompt Engineering, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Data Lake, Dataflow, CI/CD, Git, Databricks, PySpark, Power BI, Python</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09df04166b3e3f95</t>
+          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Test Automation Software Engineer Intern</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SK hynix memory solutions</t>
+          <t>Bitcot Technologies pvt ltd</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Jenkins, Git, Python, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f686645da280fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f1974e392d61c948</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Patriot Software</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, S3, Kafka, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>THORN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Git, Tableau, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, Hugging Face, FAISS, TensorFlow, PyTorch, Keras, OpenCV, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,42 +1231,1687 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d923cef69e329f</t>
+          <t>https://www.indeed.com/viewjob?jk=f44e1cea481d99be</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Programmer Analyst - Need 11+ Exp</t>
+          <t>AI DevOps Engineer - 1099 Contract</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Startekk Inc</t>
+          <t>Bitcot Technologies pvt ltd</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d73681941cc62dc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Jenkins, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Jenkins, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Jenkins, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Jenkins, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Gresham, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Jenkins, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Earth City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Jenkins, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Jenkins, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer III 4P/791</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>4P Consulting Inc.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Hugging Face, PyTorch, Kubernetes, CI/CD, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ebfc7102d473268</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Agentic Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>employers</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Pinecone, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a580c630d41e3534</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Backend</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Motive</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kinesis, Kafka, PostgreSQL, Cassandra, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40f48fc6a4776944</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior CloudOps Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CloudZero</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Gemini, Cortex, EC2, Kinesis, Kubernetes, GitHub Actions, Terraform, Git, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior CloudOps Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CloudZero</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Gemini, Cortex, EC2, Kinesis, Kubernetes, GitHub Actions, Terraform, Git, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>React Native Developer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e50cc4be98205592</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Genentech</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>12097 AI Engineer - Solutions &amp; LLMOps</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PSEG</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Newark, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=564de49a5b5ddc62</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Scientist III</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PODS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Clearwater, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, Copilot, Git, Snowflake, Databricks, PySpark, Polars, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=709632d9a8e143f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Business Analytics Advisor, Payment Integrity - Cigna Healthcare - Remote</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Chattanooga, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd99e7e9f42ab498</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Business Analytics Advisor, Payment Integrity - Cigna Healthcare - Remote</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Bloomfield, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d7c58ebb1fb5e0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Business Analytics Advisor, Payment Integrity - Cigna Healthcare - Remote</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57d66c29099f1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Business Analytics Advisor, Payment Integrity - Cigna Healthcare - Remote</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aba59ec3c425bc07</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Business Analytics Advisor, Payment Integrity - Cigna Healthcare - Remote</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c92a0293dbcae74d</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Business Analytics Advisor, Payment Integrity - Cigna Healthcare - Remote</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5da46e4167741903</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Clockwork</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d872e1bc5dfddb0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, AIOps and Observability</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Docker, Kubernetes, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=560d6f328677c4aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Knowledge Graph Developer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>United Airlines</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior AWS Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>J2B GLOBAL LLC</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, S3, EC2, Kubernetes, Terraform, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06d970472b3ef682</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Application Security Engineer-68257</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Hitachi Energy</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>Dallas, TX, US USA</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Software Engineer, Infrastructure</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Gray Swan AI</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91e8df3f654f2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Engineer, Infrastructure</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Gray Swan AI</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b5e1a3c8a5a93b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Veeva Systems</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git, Databricks, R, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=062c0655e88cc4c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Application Security Engineer-68257</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5259d199d57d6f49</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Oracle PL/SQL Developer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>C-4 Analytics</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Wakefield, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, MongoDB, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49dd3377114bd766</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full Stack (Java &amp; Kafka) (Cloud Operations Resilience Engineering)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Information Technology Senior Management Forum</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24142cc37c8959cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full Stack (Java &amp; Kafka) (Cloud Operations Resilience Engineering)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Information Technology Senior Management Forum</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Riverwoods, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=407a3f370263fabd</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PODS</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Clearwater, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Data Scientist, Copilot, Git, Snowflake, Databricks, Python, SQL, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e310e651aefb833</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
         <v>10</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb99b85db38b93a3</t>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdd1d63a4754027e</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Sr. Engineer - Tech Inventory Engineering (Frontend)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, AKS, CI/CD, PostgreSQL, MongoDB, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=152847cdc4f5d8c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics Developer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Wet Coast Logistics</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Databricks, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caf7ce376fe570cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AI/ML Silicon Verification Solutions Engineer – Tools</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d91801c00885f5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Knowledge Graph Data Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6186e9585897daa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Embedded Software Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6718bed619bc45bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>12096 AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PSEG</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Newark, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0dde69dbc7b5a9e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Fall 2027 Advisory Associate</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Berkeley Research Group, LLC</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d7db457d01c142a</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Software Engineer - Efficiency Engineering and AI Enablement</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Millennium Management</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, FastAPI, Docker, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d090cec62a340805</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Qcells</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Cartersville, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a18289d70d7b85f9</t>
         </is>
       </c>
     </row>
